--- a/swarajya-create/consultant-management/test_data/Create-Consultant-Management.xlsx
+++ b/swarajya-create/consultant-management/test_data/Create-Consultant-Management.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positive_Tests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Negative_Tests" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Positive_Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Negative_Tests" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,22 +30,20 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0362C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,28 +60,19 @@
         <fgColor rgb="00F2F6FC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE8E6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -103,33 +92,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -509,286 +495,393 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pre-condition</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Automation Status</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Execution Type</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Test Status</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks / Defect Observed</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_POS_01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Verify navigation to Consultant Dashboard</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Finance
 2. Click on the Consultant Dashboard icon</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Fetch from excel</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>User successfully navigates to the Consultant Dashboard page.</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="159.5" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="43.5" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_POS_02</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Verify existing consultant records are displayed correctly on the Consultant Dashboard</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Consultant records already exist in the system</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1. Navigate to Consultant Dashboard
+2. Observe the Consultant Details table</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Fetch from excel</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Table displays consultant records with #, Consultant Name, Phone, Personal Email, Monthly Fees, TDS %, Bank Name, Account Number, Status and Actions columns populated correctly.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="72.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Add Consultant' form opens with all expected fields</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>User is on the Consultant Dashboard page</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'New Consultant' button</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Fetch from excel</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>'Add Consultant' page opens showing Personal Details, Payment Details and Status sections with all expected input fields (First/Middle/Last Name, Phone, Personal Email, Address, Monthly Fees, TDS Percentage, Bank Name, Account Number, IFSC Code, Bank Branch, Account Type, Active).</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="159.5" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Create new consultant with mandatory fields</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>User is on Consultant Dashboard page</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>1. Click on 'New Consultant'
 2. Enter all mandatory input fields (First Name, Last Name, Phone, Personal Email, Monthly Fees, TDS Percentage, Bank Name, Account Number, IFSC Code, Account Type)
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Rohan'
-   • Last Name: 'Deshmukh'
-   • Phone: '9822334455'
-   • Personal Email: 'rohan.d@gmail.com'
-   • Monthly Fees: 40000
-   • TDS Percentage: 2
-   • Bank Name: 'HDFC Bank'
-   • Account Number: '50100234567890'
-   • IFSC Code: 'HDFC0001234'
-   • Account Type: 'Savings'
-   • Active: Ticked</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Rohan'
+Last Name: 'Deshmukh'
+Phone: '9822334455'
+Personal Email: 'rohan.d@gmail.com'
+Monthly Fees: 40000
+TDS Percentage: 2
+Bank Name: 'HDFC Bank'
+Account Number: '50100234567890'
+IFSC Code: 'HDFC0001234'
+Account Type: 'Savings'
+Active: Ticked</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>UI: Success message displayed and consultant created.</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="159.5" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_03</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="159.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Verify consultant creation save and confirmation popup</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page with mandatory fields filled</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>1. Click 'Save'
 2. Click 'Yes' on the confirmation pop-up</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Rohan'
-   • Last Name: 'Deshmukh'
-   • Phone: '9822334455'
-   • Personal Email: 'rohan.d@gmail.com'
-   • Monthly Fees: 40000
-   • TDS Percentage: 2
-   • Bank Name: 'HDFC Bank'
-   • Account Number: '50100234567890'
-   • IFSC Code: 'HDFC0001234'
-   • Account Type: 'Savings'
-   • Active: Ticked</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Rohan'
+Last Name: 'Deshmukh'
+Phone: '9822334455'
+Personal Email: 'rohan.d@gmail.com'
+Monthly Fees: 40000
+TDS Percentage: 2
+Bank Name: 'HDFC Bank'
+Account Number: '50100234567890'
+IFSC Code: 'HDFC0001234'
+Account Type: 'Savings'
+Active: Ticked</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Confirmation snackbar is displayed and new consultant is created successfully.</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="43.5" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_04</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="43.5" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Validate new consultant is listed in Consultant Dashboard via search</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>New consultant 'Rohan Deshmukh' has been created</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Consultant Dashboard page
 2. Enter 'Rohan Deshmukh' in the search bar
 3. Click 'Search' or press Enter</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Search Term: 'Rohan Deshmukh'</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>The newly created consultant 'Rohan Deshmukh' is listed in the Consultant Dashboard page.</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="203" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_05</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="203" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Verify successful consultant creation with optional Middle Name, Address and Bank Branch filled</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Finance &gt; Consultant Dashboard.
 2. Click 'New Consultant'.
@@ -797,62 +890,63 @@
 5. Click 'Yes' on the confirmation pop-up.</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Anita'
-   • Middle Name: 'Suresh'
-   • Last Name: 'Joshi'
-   • Address: '221 MG Road, Nashik'
-   • Phone: '9876501234'
-   • Personal Email: 'anita.joshi@gmail.com'
-   • Monthly Fees: 30000
-   • TDS Percentage: 2
-   • Bank Name: 'SBI'
-   • Account Number: '20456789012'
-   • IFSC Code: 'SBIN0011223'
-   • Bank Branch: 'Nashik Road'
-   • Account Type: 'Savings'
-   • Active: Ticked</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Anita'
+Middle Name: 'Suresh'
+Last Name: 'Joshi'
+Address: '221 MG Road, Nashik'
+Phone: '9876501234'
+Personal Email: 'anita.joshi@gmail.com'
+Monthly Fees: 30000
+TDS Percentage: 2
+Bank Name: 'SBI'
+Account Number: '20456789012'
+IFSC Code: 'SBIN0011223'
+Bank Branch: 'Nashik Road'
+Account Type: 'Savings'
+Active: Ticked</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Confirmation snackbar is displayed and new consultant is created successfully.</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="87" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_06</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="87" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Verify Cancel button functionality during consultant creation</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Finance &gt; Consultant Dashboard.
 2. Click 'New Consultant'.
@@ -860,54 +954,55 @@
 4. Click 'Cancel'.</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Test'
-   • Last Name: 'Cancel'
-   • Phone: '9000011111'
-   • Personal Email: 'testcancel@example.com'
-   • Monthly Fees: 25000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Test'
+Last Name: 'Cancel'
+Phone: '9000011111'
+Personal Email: 'testcancel@example.com'
+Monthly Fees: 25000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>User is returned back to the Consultant Dashboard page without creating a new consultant.</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="159.5" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_07</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="159.5" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Verify successful consultant creation with 'Active' unticked and optional fields left blank</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Consultant Dashboard.
 2. Click 'New Consultant'.
@@ -917,59 +1012,60 @@
 6. Click 'Yes' on confirmation.</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Dormant'
-   • Last Name: 'Consultant'
-   • Phone: '9111122223'
-   • Personal Email: 'dormant@example.com'
-   • Monthly Fees: 15000
-   • TDS Percentage: 2
-   • Bank Name: 'ICICI Bank'
-   • Account Number: '000123456789'
-   • IFSC Code: 'ICIC0000456'
-   • Account Type: 'Savings'
-   • Active: Unticked</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Dormant'
+Last Name: 'Consultant'
+Phone: '9111122223'
+Personal Email: 'dormant@example.com'
+Monthly Fees: 15000
+TDS Percentage: 2
+Bank Name: 'ICICI Bank'
+Account Number: '000123456789'
+IFSC Code: 'ICIC0000456'
+Account Type: 'Savings'
+Active: Unticked</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>UI: Success message displayed and consultant created as Inactive.</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="101.5" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_08</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="101.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Verify selecting 'No' on confirmation pop-up returns to Add Consultant page</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Finance &gt; Consultant Dashboard.
 2. Click 'New Consultant'.
@@ -978,55 +1074,56 @@
 5. Click 'No' on the confirmation pop-up.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Cancelled'
-   • Last Name: 'Consultant'
-   • Phone: '9000000001'
-   • Personal Email: 'cancel@test.com'
-   • Monthly Fees: 20000
-   • TDS Percentage: 2
-   • Active: Ticked</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Cancelled'
+Last Name: 'Consultant'
+Phone: '9000000001'
+Personal Email: 'cancel@test.com'
+Monthly Fees: 20000
+TDS Percentage: 2
+Active: Ticked</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>User returns to the Add Consultant page without creating a new consultant.</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_09</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Verify new inactive consultant is listed on Consultant Dashboard by searching with 'Include Inactive Consultant' ticked</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>New inactive consultant has been created.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Consultant Dashboard page.
 2. Tick the 'Include Inactive Consultant' checkbox.
@@ -1034,50 +1131,51 @@
 4. Click 'Search' or press Enter.</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Search Term: 'Dormant Consultant'
-   • Include Inactive Consultant: Ticked</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Search Term: 'Dormant Consultant'
+Include Inactive Consultant: Ticked</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>The newly created inactive consultant is listed on the Consultant Dashboard page.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="145" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_10</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="145" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Verify creation with exactly maximum allowed characters in all text fields</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1. Fill First Name with exactly 100 characters.
 2. Fill other mandatory fields.
@@ -1085,58 +1183,59 @@
 4. Click 'Yes' on confirmation.</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'A' (100 times)
-   • Last Name: 'MaxChar'
-   • Phone: '9999999999'
-   • Personal Email: 'maxchar@example.com'
-   • Monthly Fees: 50000
-   • TDS Percentage: 2
-   • Bank Name: 'Axis Bank'
-   • Account Number: '910100234567'
-   • IFSC Code: 'UTIB0001234'
-   • Account Type: 'Savings'</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'A' (100 times)
+Last Name: 'MaxChar'
+Phone: '9999999999'
+Personal Email: 'maxchar@example.com'
+Monthly Fees: 50000
+TDS Percentage: 2
+Bank Name: 'Axis Bank'
+Account Number: '910100234567'
+IFSC Code: 'UTIB0001234'
+Account Type: 'Savings'</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Consultant is created successfully.</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="87" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_11</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="87" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Verify leading and trailing whitespaces are trimmed from input fields upon saving</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>1. Enter First Name with leading and trailing spaces.
 2. Fill other mandatory fields.
@@ -1144,54 +1243,55 @@
 4. Click 'Yes' on confirmation.</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: '   Space   '
-   • Last Name: '   Trim   '
-   • Phone: '9888877776'
-   • Personal Email: 'spacetrim@example.com'
-   • Monthly Fees: 22000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>First Name: '   Space   '
+Last Name: '   Trim   '
+Phone: '9888877776'
+Personal Email: 'spacetrim@example.com'
+Monthly Fees: 22000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Consultant is created successfully and name is saved as 'Space' and 'Trim' without leading/trailing spaces.</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="72.5" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_12</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="72.5" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Verify existing consultant details can be edited via the Actions edit icon</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>An active consultant exists on the Consultant Dashboard (e.g. 'Satish Patil').</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Consultant Dashboard.
 2. Click the edit (pencil) icon against a consultant row.
@@ -1200,99 +1300,101 @@
 5. Click 'Yes' on confirmation.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Consultant: 'Satish Patil'
-   • Updated Monthly Fees: 55000
-   • Updated TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Consultant: 'Satish Patil'
+Updated Monthly Fees: 55000
+Updated TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Confirmation snackbar is displayed and updated details are reflected in the Consultant Dashboard row.</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_13</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Verify Account Number is masked on Consultant Dashboard</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Consultants with saved bank account numbers exist.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Consultant Dashboard.
 2. Observe the Account Number column for existing consultants.</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fetch from excel</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Account Number is masked, showing only the last 4 digits (e.g. '*****5678').</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="72.5" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_14</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="72.5" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_16</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Verify Status toggle changes consultant from Active to Inactive</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>An active consultant exists on the Consultant Dashboard.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Consultant Dashboard.
 2. Click the edit icon for the consultant.
@@ -1301,79 +1403,353 @@
 5. Click 'Yes' on confirmation.</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Consultant: 'Ravindra Maruti Patil'
-   • Active: Unticked</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Consultant: 'Ravindra Maruti Patil'
+Active: Unticked</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Consultant Status changes to 'Inactive' and consultant no longer appears in the default (Active-only) list.</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>TC_CONSULTANT_POS_15</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="43.5" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Verify pagination works correctly on Consultant Dashboard</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>More than the default 'Items per page' consultants exist.</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Consultant Dashboard.
 2. Set 'Items per page' to a smaller value (e.g. 5).
 3. Click the next page arrow.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Items per page: 5</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Dashboard correctly paginates and displays the next set of consultant records, with the record count updated (e.g. '6 - 10 of X').</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_18</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Verify TDS Percentage is always saved and displayed as a valid numeric value</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>A consultant is created with a valid TDS Percentage</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>1. Create/open a consultant with TDS Percentage = 2
+2. Navigate to Consultant Dashboard
+3. Observe the TDS % column for that consultant</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Consultant: 'Ravindra Maruti Patil'
+TDS Percentage entered: 2</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>TDS % column displays a valid numeric percentage (e.g. '2%') for every consultant record.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): On the live Consultant Dashboard, 'Ravindra Maruti Patil' (row #2) shows only '%' with no numeric value in the TDS % column, indicating the value was not saved/rendered correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Verify Account Number masking format is consistent across all consultant records</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Multiple consultants with account numbers of different lengths exist</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Consultant Dashboard
+2. Compare the Account Number column formatting across all rows</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Fetch from excel</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>All Account Numbers follow the same masking pattern (e.g. always show only the last 4 digits, rest masked with a fixed number of asterisks), regardless of the underlying account number length.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): Masking is inconsistent - '*****5678' (5 asterisks) vs '*********8006' (9 asterisks) vs '****************1112' (16 asterisks) - full account number length is effectively exposed via mask length, which is a data-masking/security defect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_20</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Verify Bank Name field only stores the bank's name and not account/branch codes</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>User creates or views a consultant with Payment Details filled</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>1. Create a consultant, entering a valid Bank Name (e.g. 'ICICI Bank')
+2. Navigate to Consultant Dashboard
+3. Observe the Bank Name column</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Consultant: 'Sooraj Chandrakant Chavan'
+Bank Name entered: 'ICICI Bank'</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Bank Name column displays only the bank's name (e.g. 'ICICI Bank') consistently for every record.</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): 'Sooraj Chandrakant Chavan' shows Bank Name as 'ICICI0000005', which looks like a branch/IFSC-style code rather than a bank name - suggests missing field-level validation or a field mapping issue on save.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="43.5" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Verify Consultant Name fields do not allow numeric characters</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>User is on the 'Add Consultant' page</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1. Create a consultant with alphabetic-only First/Middle/Last Name
+2. Save the consultant
+3. Verify the name on the Consultant Dashboard</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Ravindra'
+Middle Name: 'Maruti'
+Last Name: 'Patil'</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Consultant Name is saved and displayed using only alphabetic characters, matching what was intended to be entered.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): Existing record 'Ravindra1 Maruti2 Patil1' (row #3) shows digits embedded within First/Middle/Last Name, confirming the Name fields do not currently block numeric input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43.5" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_POS_22</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Verify Monthly Fees enforces a sensible minimum value on save</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>User is on the 'Add Consultant' page</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt to create a consultant with a very low Monthly Fees value (e.g. below the firm's configured minimum, say Rs.5,000)
+2. Click 'Save'</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Monthly Fees: 1000</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>System either blocks the save with a validation message (e.g. 'Monthly Fees must be at least Rs.5,000') or requires explicit confirmation before accepting an unusually low fee.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): Live data shows consultants saved with Monthly Fees as low as 1000 and 2000 with no warning, indicating no minimum-value validation is enforced.</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1400,292 +1776,302 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pre-condition</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Automation Status</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Execution Type</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Test Status</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks / Defect Observed</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="145" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Attempt to create consultant with blank mandatory fields</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>1. Click on 'New Consultant'
 2. Leave mandatory fields (First Name, Last Name, Phone, Personal Email, Monthly Fees, TDS Percentage, Bank Name, Account Number, IFSC Code, Account Type) blank
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: ''
-   • Last Name: ''
-   • Phone: ''
-   • Personal Email: ''
-   • Monthly Fees: ''
-   • TDS Percentage: ''
-   • Bank Name: ''
-   • Account Number: ''
-   • IFSC Code: ''
-   • Account Type: ''</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>First Name: ''
+Last Name: ''
+Phone: ''
+Personal Email: ''
+Monthly Fees: ''
+TDS Percentage: ''
+Bank Name: ''
+Account Number: ''
+IFSC Code: ''
+Account Type: ''</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>UI: Validation error messages displayed against each blank mandatory field, e.g. "First Name can't be blank.", "Phone can't be blank."</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="87" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_02</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Attempt to create consultant with existing duplicate Personal Email</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page. A consultant with email 'satish@gmail.com' exists.</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>1. Click on 'New Consultant'
 2. Enter an existing Personal Email
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Duplicate'
-   • Last Name: 'Email'
-   • Phone: '9812345670'
-   • Personal Email: 'satish@gmail.com'
-   • Monthly Fees: 25000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Duplicate'
+Last Name: 'Email'
+Phone: '9812345670'
+Personal Email: 'satish@gmail.com'
+Monthly Fees: 25000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>UI: Error message 'Consultant with this email already exists' displayed.</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="87" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_03</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Attempt to create consultant with SQL injection payload in First Name</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>1. Click on 'New Consultant'
 2. Enter SQL injection string in First Name
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: "Robert'); DROP TABLE Consultants;--"
-   • Last Name: 'Test'
-   • Phone: '9800012345'
-   • Personal Email: 'sqlinject@example.com'
-   • Monthly Fees: 20000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>First Name: "Robert'); DROP TABLE Consultants;--"
+Last Name: 'Test'
+Phone: '9800012345'
+Personal Email: 'sqlinject@example.com'
+Monthly Fees: 20000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>UI: Payload is sanitized or rejected with a generic error. No database impact occurs.</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="116" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_04</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Attempt to create consultant with First Name exceeding maximum character length</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>1. Click on 'New Consultant'
 2. Enter First Name &gt; 100 characters
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'This is a very long consultant first name that exceeds the maximum allowed character limit of one hundred characters for this input field'
-   • Last Name: 'Long'
-   • Phone: '9876543210'
-   • Personal Email: 'longname@example.com'
-   • Monthly Fees: 20000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'This is a very long consultant first name that exceeds the maximum allowed character limit of one hundred characters for this input field'
+Last Name: 'Long'
+Phone: '9876543210'
+Personal Email: 'longname@example.com'
+Monthly Fees: 20000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>UI: Validation error message 'First Name exceeds maximum length' displayed.</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="87" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_05</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Attempt to create a consultant with an invalid Personal Email format</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Consultant'.
 2. Enter valid mandatory details.
@@ -1693,54 +2079,55 @@
 4. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Tech'
-   • Last Name: 'Solutions'
-   • Phone: '9555123456'
-   • Personal Email: 'invalid.email.format'
-   • Monthly Fees: 30000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Tech'
+Last Name: 'Solutions'
+Phone: '9555123456'
+Personal Email: 'invalid.email.format'
+Monthly Fees: 30000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>UI: Validation error 'Please enter a valid email address' is displayed.</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="87" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_06</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Attempt to create a consultant with invalid (non-numeric) characters in the Phone field</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>1. Click 'New Consultant'.
 2. Enter valid mandatory details.
@@ -1748,54 +2135,55 @@
 4. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Alpha'
-   • Last Name: 'Corp'
-   • Phone: 'ABC-123-XYZ'
-   • Personal Email: 'alpha@example.com'
-   • Monthly Fees: 28000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Alpha'
+Last Name: 'Corp'
+Phone: 'ABC-123-XYZ'
+Personal Email: 'alpha@example.com'
+Monthly Fees: 28000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>UI: Validation error 'Phone number can only contain digits' is displayed.</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="101.5" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_07</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Verify consultant is not created when clicking 'No' on the confirmation pop-up</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Finance &gt; Consultant Dashboard.
 2. Click 'New Consultant'.
@@ -1804,103 +2192,105 @@
 5. Click 'No' (or dismiss) on the confirmation pop-up.</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'No'
-   • Last Name: 'Confirm'
-   • Phone: '9611234567'
-   • Personal Email: 'noconfirm@consultant.com'
-   • Monthly Fees: 18000
-   • TDS Percentage: 2
-   • Active: Ticked</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'No'
+Last Name: 'Confirm'
+Phone: '9611234567'
+Personal Email: 'noconfirm@consultant.com'
+Monthly Fees: 18000
+TDS Percentage: 2
+Active: Ticked</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Pop-up is closed. User remains on the 'Add Consultant' page and consultant is not created.</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_08</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Verify navigation fails if user is not logged in as Admin</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>User is logged in as a non-Admin user</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Finance
 2. Attempt to click on the Consultant Dashboard icon</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Consultant Dashboard icon is not visible or access is denied.</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="145" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_09</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Attempt to create consultant with an invalid IFSC Code format</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Consultant'.
 2. Fill valid mandatory details.
@@ -1908,632 +2298,938 @@
 4. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'IFSC'
-   • Last Name: 'Test'
-   • Phone: '9723456789'
-   • Personal Email: 'ifsctest@example.com'
-   • Monthly Fees: 24000
-   • TDS Percentage: 2
-   • Bank Name: 'HDFC Bank'
-   • Account Number: '50100234567890'
-   • IFSC Code: '12345INVALID'
-   • Account Type: 'Savings'</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'IFSC'
+Last Name: 'Test'
+Phone: '9723456789'
+Personal Email: 'ifsctest@example.com'
+Monthly Fees: 24000
+TDS Percentage: 2
+Bank Name: 'HDFC Bank'
+Account Number: '50100234567890'
+IFSC Code: '12345INVALID'
+Account Type: 'Savings'</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>UI: Validation error 'Please enter a valid IFSC code' displayed. Consultant is not created.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="101.5" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_10</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Attempt to create consultant with non-alphabetic characters in First Name, Last Name and Bank Name</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1. Click 'New Consultant'
 2. Enter numeric/special characters in First Name, Last Name and Bank Name
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Rohan123!'
-   • Last Name: 'D3shmukh'
-   • Phone: '9812309876'
-   • Personal Email: 'rohan123@example.com'
-   • Monthly Fees: 26000
-   • TDS Percentage: 2
-   • Bank Name: 'HDFC@123'</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Rohan123!'
+Last Name: 'D3shmukh'
+Phone: '9812309876'
+Personal Email: 'rohan123@example.com'
+Monthly Fees: 26000
+TDS Percentage: 2
+Bank Name: 'HDFC@123'</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>UI: Validation errors displayed for non-alphabetic input in Name and Bank Name fields.</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="101.5" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_11</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Attempt to create consultant with non-numeric characters in Monthly Fees, TDS Percentage and Account Number</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Consultant'
 2. Enter alphabetic/special characters in Monthly Fees, TDS Percentage and Account Number
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Non'
-   • Last Name: 'Numeric'
-   • Phone: '9834567890'
-   • Personal Email: 'nonnumeric@example.com'
-   • Monthly Fees: 'Forty Thousand'
-   • TDS Percentage: 'Two'
-   • Account Number: 'ABCD1234EFGH'</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Non'
+Last Name: 'Numeric'
+Phone: '9834567890'
+Personal Email: 'nonnumeric@example.com'
+Monthly Fees: 'Forty Thousand'
+TDS Percentage: 'Two'
+Account Number: 'ABCD1234EFGH'</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>UI: Validation errors displayed for non-numeric input in Monthly Fees, TDS Percentage and Account Number fields.</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="87" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_12</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Attempt to create consultant with TDS Percentage &gt; 100% or &lt; 0%</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1. Enter valid mandatory fields.
 2. Enter '105' in TDS Percentage field.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Percent'
-   • Last Name: 'Test'
-   • Phone: '9845678901'
-   • Personal Email: 'percent@example.com'
-   • Monthly Fees: 20000
-   • TDS Percentage: 105</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Percent'
+Last Name: 'Test'
+Phone: '9845678901'
+Personal Email: 'percent@example.com'
+Monthly Fees: 20000
+TDS Percentage: 105</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Error message displayed indicating TDS Percentage must be between 0 and 100. Consultant is not created.</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="87" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_13</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Attempt to create a consultant with negative Monthly Fees</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>1. Enter valid mandatory fields.
 2. Enter '-5000' in Monthly Fees field.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Negative'
-   • Last Name: 'Fees'
-   • Phone: '9856789012'
-   • Personal Email: 'negfees@example.com'
-   • Monthly Fees: -5000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Negative'
+Last Name: 'Fees'
+Phone: '9856789012'
+Personal Email: 'negfees@example.com'
+Monthly Fees: -5000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Error message displayed indicating Monthly Fees cannot be negative. Consultant is not created.</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="87" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_14</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Attempt to create a consultant with an XSS payload in the First Name field</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Enter XSS payload in First Name.
 2. Fill other mandatory fields.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: '&lt;script&gt;alert("XSS")&lt;/script&gt;'
-   • Last Name: 'Test'
-   • Phone: '9867890123'
-   • Personal Email: 'xss@example.com'
-   • Monthly Fees: 21000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>First Name: '&lt;script&gt;alert("XSS")&lt;/script&gt;'
+Last Name: 'Test'
+Phone: '9867890123'
+Personal Email: 'xss@example.com'
+Monthly Fees: 21000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>System sanitizes the input or rejects it with an error. No script is executed.</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="101.5" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_15</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Attempt to create consultant with an Account Number shorter than the minimum allowed length</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>1. Enter valid mandatory fields.
 2. Enter a 3-digit Account Number.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Short'
-   • Last Name: 'Account'
-   • Phone: '9878901234'
-   • Personal Email: 'shortacc@example.com'
-   • Monthly Fees: 23000
-   • TDS Percentage: 2
-   • Account Number: '123'</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Short'
+Last Name: 'Account'
+Phone: '9878901234'
+Personal Email: 'shortacc@example.com'
+Monthly Fees: 23000
+TDS Percentage: 2
+Account Number: '123'</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>UI: Validation error 'Account Number is too short' displayed. Consultant is not created.</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="87" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_16</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Attempt to create consultant after session timeout exceeds</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>1. Fill consultant details
 2. Wait for session to timeout
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Timeout'
-   • Last Name: 'Consultant'
-   • Phone: '9889012345'
-   • Personal Email: 'timeout@example.com'
-   • Monthly Fees: 27000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Timeout'
+Last Name: 'Consultant'
+Phone: '9889012345'
+Personal Email: 'timeout@example.com'
+Monthly Fees: 27000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>UI: User is redirected to login page with a timeout message.</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="87" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_17</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Attempt to create consultant when network is idle or server is down</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin, on Add Consultant page, and network is disconnected/server is down.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1. Fill consultant details
 2. Disconnect network/simulate server down
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Network'
-   • Last Name: 'Idle'
-   • Phone: '9890123456'
-   • Personal Email: 'network@example.com'
-   • Monthly Fees: 29000
-   • TDS Percentage: 2</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Network'
+Last Name: 'Idle'
+Phone: '9890123456'
+Personal Email: 'network@example.com'
+Monthly Fees: 29000
+TDS Percentage: 2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>UI: 'Network error' or 'Server unreachable' message displayed. Consultant is not created.</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_18</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Validate that a consultant creation failed due to session timeout is not listed on the Consultant Dashboard</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Consultant creation failed due to session timeout (ref TC_CONSULTANT_NEG_16).</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Consultant creation failed due to session timeout.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>1. Log in again
 2. Navigate to Consultant Dashboard page
 3. Search for the consultant</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Search Term: 'Timeout Consultant'</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Consultant is not displayed in the list.</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="101.5" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_19</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Attempt to create consultant leaving Account Type dropdown unselected</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Add Consultant' page.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>1. Fill all mandatory fields except Account Type.
 2. Leave Account Type dropdown as default/unselected.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'NoType'
-   • Last Name: 'Selected'
-   • Phone: '9801122334'
-   • Personal Email: 'notype@example.com'
-   • Monthly Fees: 19000
-   • TDS Percentage: 2
-   • Account Type: ''</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'NoType'
+Last Name: 'Selected'
+Phone: '9801122334'
+Personal Email: 'notype@example.com'
+Monthly Fees: 19000
+TDS Percentage: 2
+Account Type: ''</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>UI: Validation error "Account Type can't be blank." displayed. Consultant is not created.</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="101.5" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TC_CONSULTANT_NEG_20</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Attempt to create consultant with duplicate Account Number for a different consultant</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Admin. A consultant with Account Number '50100234567890' exists.</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>1. Click 'New Consultant'
 2. Enter the existing Account Number for a new consultant
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • First Name: 'Duplicate'
-   • Last Name: 'Account'
-   • Phone: '9812233445'
-   • Personal Email: 'dupaccount@example.com'
-   • Monthly Fees: 21000
-   • TDS Percentage: 2
-   • Account Number: '50100234567890'</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Duplicate'
+Last Name: 'Account'
+Phone: '9812233445'
+Personal Email: 'dupaccount@example.com'
+Monthly Fees: 21000
+TDS Percentage: 2
+Account Number: '50100234567890'</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>UI: Error message 'Account Number already exists' displayed. Consultant is not created.</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>To Be Automated</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="101.5" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_NEG_21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Attempt to save a consultant Name containing digits (should be rejected)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>User is on the 'Add Consultant' page</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'New Consultant'
+2. Enter digits within First Name, Middle Name and Last Name
+3. Click 'Save'</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Ravindra1'
+Middle Name: 'Maruti2'
+Last Name: 'Patil1'
+Phone: '8796819111'
+Personal Email: 'ravi21711@gmail.com'
+Monthly Fees: 1000
+TDS Percentage: 6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>System should reject the entry with a validation error such as "Name can only contain alphabetic characters." and NOT create the consultant.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): This exact data is already present live as consultant 'Ravindra1 Maruti2 Patil1' (row #3), proving the system currently accepts digits in Name fields instead of rejecting them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="87" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_NEG_22</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Attempt to save a consultant leaving TDS Percentage effectively blank (should be rejected)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>User is on the 'Add Consultant' page</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>1. Click 'New Consultant'
+2. Fill mandatory fields
+3. Leave TDS Percentage field blank (or enter only non-numeric input)
+4. Click 'Save'</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Ravindra'
+Last Name: 'Patil'
+Phone: '8796819132'
+Personal Email: 'ravi21791@gmail.com'
+Monthly Fees: 2000
+TDS Percentage: ''</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>System should reject the save with a validation error such as "TDS Percentage can't be blank." and NOT create the consultant with an empty TDS value.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): Live consultant 'Ravindra Maruti Patil' (row #2) is saved and displayed with TDS % showing only '%' and no numeric value, confirming blank/invalid TDS Percentage is currently accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="101.5" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_NEG_23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Attempt to enter a non-bank-name value (account/branch style code) into the Bank Name field (should be rejected)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>User is on the 'Add Consultant' page</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'New Consultant'
+2. Fill mandatory fields
+3. Enter an account/branch code style string into Bank Name
+4. Click 'Save'</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>First Name: 'Sooraj'
+Last Name: 'Chavan'
+Phone: '8805634342'
+Personal Email: 'ash@gmail.com'
+Monthly Fees: 45000
+TDS Percentage: 2
+Bank Name: 'ICICI0000005'</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>System should reject the entry with a validation error such as "Bank Name can only contain alphabetic characters/spaces." and NOT save the record as-is.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): Live consultant 'Sooraj Chandrakant Chavan' has Bank Name saved exactly as 'ICICI0000005', confirming the Bank Name field currently accepts non-bank-name/code-style values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="72.5" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_NEG_24</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Attempt to create a near-duplicate consultant differing from an existing one only by inserted digits in Name/Phone (should be flagged)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>An active consultant 'Ravindra Maruti Patil' with Phone '8796819132' already exists</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>1. Click 'New Consultant'
+2. Enter a Name/Phone that is a near-duplicate of an existing consultant (digits inserted into name, phone off by 1-2 digits)
+3. Click 'Save'</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>First Name: 'Ravindra1'
+Middle Name: 'Maruti2'
+Last Name: 'Patil1'
+Phone: '8796819111'
+Personal Email: 'ravi21711@gmail.com'</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>System should warn the user of a potential duplicate consultant (similar name/phone to an existing active record) before allowing save, or block the save outright.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): Both 'Ravindra Maruti Patil' (#2) and 'Ravindra1 Maruti2 Patil1' (#3) exist as separate active records with near-identical names and phone numbers differing by 1-2 digits, indicating no duplicate/similarity check is performed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC_CONSULTANT_NEG_25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Attempt to save a consultant with Account Number masking that would expose the true account length (should be normalized)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>User is on the 'Add Consultant' page</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1. Create consultants with account numbers of clearly different lengths (e.g. 10 digits vs 18 digits)
+2. View both on the Consultant Dashboard
+3. Compare the number of masking asterisks shown</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Consultant A Account Number: '1234567890' (10 digits)
+Consultant B Account Number: '123456789012345678' (18 digits)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>System should apply a fixed/normalized masking pattern (e.g. always exactly 'XXXX-XXXX-1234' or a constant number of asterisks) so the true account number length cannot be inferred from the mask.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>To Be Automated</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>SUSPECTED ISSUE (pending automation verification): Existing records show masks of varying asterisk counts (5, 8, 9, 16+), meaning the raw account number length is indirectly exposed on-screen - a data-masking defect that should be fixed before this passes.</t>
         </is>
       </c>
     </row>

--- a/swarajya-create/consultant-management/test_data/Create-Consultant-Management.xlsx
+++ b/swarajya-create/consultant-management/test_data/Create-Consultant-Management.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -741,7 +741,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">

--- a/swarajya-create/consultant-management/test_data/Create-Consultant-Management.xlsx
+++ b/swarajya-create/consultant-management/test_data/Create-Consultant-Management.xlsx
@@ -2220,7 +2220,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
